--- a/crm-service/templates/customers-template.xlsx
+++ b/crm-service/templates/customers-template.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>کد اقتصادی</t>
+          <t>شماره اقتصادی</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
